--- a/files/港岛-寿臣山及浅水湾-深水湾径8号.xlsx
+++ b/files/港岛-寿臣山及浅水湾-深水湾径8号.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -112,36 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -171,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -187,42 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -589,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -598,7 +473,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -894,7 +769,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-05</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1290,7 +1165,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-11-13</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1386,7 +1261,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-03-16</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1482,7 +1357,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-06-24</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1578,7 +1453,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-02-26</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1624,7 +1499,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1670,7 +1545,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-05-15</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1766,7 +1641,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-04-01</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1862,7 +1737,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-05-15</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2208,7 +2083,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2304,7 +2179,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-02</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2600,7 +2475,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-11-15</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2646,7 +2521,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-02-04</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2742,7 +2617,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-09-07</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2788,7 +2663,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-22</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2834,7 +2709,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-11-26</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2880,7 +2755,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-02-26</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2926,7 +2801,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-07-19</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2972,7 +2847,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-11-07</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3018,7 +2893,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-11-15</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3178,6 +3053,106 @@
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>1号屋</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>12566</v>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>2号屋</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>7710</v>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -3190,824 +3165,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>深水湾径8号 - 1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>26 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>9 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>17 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>18&amp;19/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 6529呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 7070呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 3407呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 3641呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 3407呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 3641呎 (4+房)
-$39,323万
-$108,000/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 3407呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 3641呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 3407呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 3641呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 3407呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 3641呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 3407呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 3641呎 (4+房)
-$24,941万
-$68,500/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 3407呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 3641呎 (4+房)
-$25,123万
-$69,000/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 3407呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 3641呎 (4+房)
-$24,468万
-$67,200/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 3407呎 (4+房)
-$21,348万
-$62,660/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 3641呎 (4+房)
-$22,865万
-$62,800/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 3407呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 3641呎 (4+房)
-$22,865万
-$62,800/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 3407呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 3641呎 (4+房)
-$22,137万
-$60,800/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>UG&amp;1&amp;2/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 7085呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 7568呎 (4+房)
-$60,544万
-$80,000/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>深水湾径8号 - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>26 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>11 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>15 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>18&amp;19/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>C | 7937呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>D | 5785呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>C | 4214呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>D | 2865呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>C | 4214呎 (4+房)
-$45,000万
-$106,787/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>D | 2865呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>C | 4214呎 (4+房)
-$37,505万
-$89,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>D | 2865呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>C | 4214呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>D | 2865呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>C | 4214呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>D | 2865呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>C | 4214呎 (4+房)
-$31,184万
-$74,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>D | 2865呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>C | 4214呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>D | 2865呎 (3房)
-$18,622万
-$65,000/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>C | 4214呎 (4+房)
-$34,555万
-$82,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>D | 2865呎 (3房)
-$17,960万
-$62,688/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>C | 4214呎 (4+房)
-$29,203万
-$69,300/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>D | 2865呎 (3房)
-$18,050万
-$63,000/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>C | 4214呎 (4+房)
-$28,770万
-$68,272/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>D | 2865呎 (3房)
-$17,500万
-$61,082/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>C | 4214呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>D | 2865呎 (3房)
-$17,476万
-$61,000/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>UG&amp;1&amp;2/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>C | 8475呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>D | 6322呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-寿臣山及浅水湾-深水湾径8号.xlsx
+++ b/files/港岛-寿臣山及浅水湾-深水湾径8号.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +44,120 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +168,36 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -97,6 +242,69 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -474,7 +682,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -3165,4 +3373,960 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>18&amp;19</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 6529呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 7070呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 3407呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 3641呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 3407呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 3641呎 (4+房)
+$39323万
+$108,000/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 3407呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 3641呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 3407呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 3641呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 3407呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 3641呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 3407呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 3641呎 (4+房)
+$24941万
+$68,500/呎
+(18年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 3407呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 3641呎 (4+房)
+$25123万
+$69,000/呎
+(21年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 3407呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 3641呎 (4+房)
+$24468万
+$67,200/呎
+(19年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 3407呎 (4+房)
+$21348万
+$62,660/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 3641呎 (4+房)
+$22865万
+$62,800/呎
+(19年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 3407呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 3641呎 (4+房)
+$22865万
+$62,800/呎
+(19年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 3407呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 3641呎 (4+房)
+$22137万
+$60,800/呎
+(19年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>UG&amp;1&amp;2</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 7085呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 7568呎 (4+房)
+$60544万
+$80,000/呎
+(19年-05月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>18&amp;19</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>C | 7937呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>D | 5785呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>C | 4214呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>D | 2865呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>C | 4214呎 (4+房)
+$45000万
+$106,787/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>D | 2865呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>C | 4214呎 (4+房)
+$37505万
+$89,000/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>D | 2865呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>C | 4214呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>D | 2865呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>C | 4214呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>D | 2865呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>C | 4214呎 (4+房)
+$31184万
+$74,000/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>D | 2865呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>C | 4214呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>D | 2865呎 (3房)
+$18622万
+$65,000/呎
+(21年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>C | 4214呎 (4+房)
+$34555万
+$82,000/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>D | 2865呎 (3房)
+$17960万
+$62,688/呎
+(20年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>C | 4214呎 (4+房)
+$29203万
+$69,300/呎
+(19年-02月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>D | 2865呎 (3房)
+$18050万
+$63,000/呎
+(20年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>C | 4214呎 (4+房)
+$28770万
+$68,272/呎
+(18年-11月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>D | 2865呎 (3房)
+$17500万
+$61,082/呎
+(20年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>C | 4214呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>D | 2865呎 (3房)
+$17476万
+$61,000/呎
+(20年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>UG&amp;1&amp;2</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>C | 8475呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>D | 6322呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>深水湾径8号 - 独立屋销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>2 套</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="D3" s="25" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="E3" s="26" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="F3" s="22" t="inlineStr">
+        <is>
+          <t>2 套</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>类型/位置</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>1号屋</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2号屋</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>独立屋</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>1号屋
+12566呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>2号屋
+7710呎 (3房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-寿臣山及浅水湾-深水湾径8号.xlsx
+++ b/files/港岛-寿臣山及浅水湾-深水湾径8号.xlsx
@@ -682,7 +682,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-寿臣山及浅水湾-深水湾径8号.xlsx
+++ b/files/港岛-寿臣山及浅水湾-深水湾径8号.xlsx
@@ -672,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:N56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -685,6 +685,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -742,6 +746,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -792,6 +816,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -842,6 +886,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -892,6 +956,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -942,6 +1026,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -988,6 +1092,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1038,6 +1162,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1088,6 +1232,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1138,6 +1302,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1188,6 +1372,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1238,6 +1442,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1288,6 +1512,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1338,6 +1582,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1384,6 +1648,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1434,6 +1718,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1480,6 +1784,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1530,6 +1854,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1576,6 +1920,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1626,6 +1990,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1672,6 +2056,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1718,6 +2122,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1764,6 +2188,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1814,6 +2258,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1860,6 +2324,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1910,6 +2394,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1956,6 +2460,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2006,6 +2530,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2056,6 +2600,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2106,6 +2670,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2156,6 +2740,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2206,6 +2810,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2256,6 +2880,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2302,6 +2946,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2352,6 +3016,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2398,6 +3082,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2448,6 +3152,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2498,6 +3222,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2548,6 +3292,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2598,6 +3362,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2648,6 +3432,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2694,6 +3498,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2740,6 +3564,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2790,6 +3634,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2836,6 +3700,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2882,6 +3766,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2928,6 +3832,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2974,6 +3898,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3020,6 +3964,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3066,6 +4030,26 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3112,6 +4096,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3162,6 +4166,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3212,6 +4236,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3262,6 +4306,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3312,6 +4376,26 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3362,13 +4446,33 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -3542,7 +4646,7 @@
           <t>B | 3641呎 (4+房)
 $39323万
 $108,000/呎
-(22年-01月)</t>
+(22年-01月-05日)</t>
         </is>
       </c>
     </row>
@@ -3634,7 +4738,7 @@
           <t>B | 3641呎 (4+房)
 $24941万
 $68,500/呎
-(18年-11月)</t>
+(18年-11月-13日)</t>
         </is>
       </c>
     </row>
@@ -3657,7 +4761,7 @@
           <t>B | 3641呎 (4+房)
 $25123万
 $69,000/呎
-(21年-03月)</t>
+(21年-03月-16日)</t>
         </is>
       </c>
     </row>
@@ -3680,7 +4784,7 @@
           <t>B | 3641呎 (4+房)
 $24468万
 $67,200/呎
-(19年-06月)</t>
+(19年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -3695,7 +4799,7 @@
           <t>A | 3407呎 (4+房)
 $21348万
 $62,660/呎
-(25年-06月)</t>
+(25年-06月-04日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -3703,7 +4807,7 @@
           <t>B | 3641呎 (4+房)
 $22865万
 $62,800/呎
-(19年-02月)</t>
+(19年-02月-26日)</t>
         </is>
       </c>
     </row>
@@ -3726,7 +4830,7 @@
           <t>B | 3641呎 (4+房)
 $22865万
 $62,800/呎
-(19年-05月)</t>
+(19年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -3749,7 +4853,7 @@
           <t>B | 3641呎 (4+房)
 $22137万
 $60,800/呎
-(19年-04月)</t>
+(19年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -3772,7 +4876,7 @@
           <t>B | 7568呎 (4+房)
 $60544万
 $80,000/呎
-(19年-05月)</t>
+(19年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -3944,7 +5048,7 @@
           <t>C | 4214呎 (4+房)
 $45000万
 $106,787/呎
-(21年-10月)</t>
+(21年-10月-20日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -3967,7 +5071,7 @@
           <t>C | 4214呎 (4+房)
 $37505万
 $89,000/呎
-(21年-05月)</t>
+(21年-05月-02日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -4036,7 +5140,7 @@
           <t>C | 4214呎 (4+房)
 $31184万
 $74,000/呎
-(18年-11月)</t>
+(18年-11月-15日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -4067,7 +5171,7 @@
           <t>D | 2865呎 (3房)
 $18622万
 $65,000/呎
-(21年-02月)</t>
+(21年-02月-04日)</t>
         </is>
       </c>
     </row>
@@ -4082,7 +5186,7 @@
           <t>C | 4214呎 (4+房)
 $34555万
 $82,000/呎
-(21年-08月)</t>
+(21年-08月-22日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -4090,7 +5194,7 @@
           <t>D | 2865呎 (3房)
 $17960万
 $62,688/呎
-(20年-09月)</t>
+(20年-09月-07日)</t>
         </is>
       </c>
     </row>
@@ -4105,7 +5209,7 @@
           <t>C | 4214呎 (4+房)
 $29203万
 $69,300/呎
-(19年-02月)</t>
+(19年-02月-26日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -4113,7 +5217,7 @@
           <t>D | 2865呎 (3房)
 $18050万
 $63,000/呎
-(20年-11月)</t>
+(20年-11月-26日)</t>
         </is>
       </c>
     </row>
@@ -4128,7 +5232,7 @@
           <t>C | 4214呎 (4+房)
 $28770万
 $68,272/呎
-(18年-11月)</t>
+(18年-11月-07日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -4136,7 +5240,7 @@
           <t>D | 2865呎 (3房)
 $17500万
 $61,082/呎
-(20年-07月)</t>
+(20年-07月-19日)</t>
         </is>
       </c>
     </row>
@@ -4159,7 +5263,7 @@
           <t>D | 2865呎 (3房)
 $17476万
 $61,000/呎
-(20年-11月)</t>
+(20年-11月-15日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-寿臣山及浅水湾-深水湾径8号.xlsx
+++ b/files/港岛-寿臣山及浅水湾-深水湾径8号.xlsx
@@ -4646,7 +4646,7 @@
           <t>B | 3641呎 (4+房)
 $39323万
 $108,000/呎
-(22年-01月-05日)</t>
+(22年-01月)</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
           <t>B | 3641呎 (4+房)
 $24941万
 $68,500/呎
-(18年-11月-13日)</t>
+(18年-11月)</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
           <t>B | 3641呎 (4+房)
 $25123万
 $69,000/呎
-(21年-03月-16日)</t>
+(21年-03月)</t>
         </is>
       </c>
     </row>
@@ -4784,7 +4784,7 @@
           <t>B | 3641呎 (4+房)
 $24468万
 $67,200/呎
-(19年-06月-24日)</t>
+(19年-06月)</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
           <t>A | 3407呎 (4+房)
 $21348万
 $62,660/呎
-(25年-06月-04日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -4807,7 +4807,7 @@
           <t>B | 3641呎 (4+房)
 $22865万
 $62,800/呎
-(19年-02月-26日)</t>
+(19年-02月)</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
           <t>B | 3641呎 (4+房)
 $22865万
 $62,800/呎
-(19年-05月-15日)</t>
+(19年-05月)</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
           <t>B | 3641呎 (4+房)
 $22137万
 $60,800/呎
-(19年-04月-01日)</t>
+(19年-04月)</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
           <t>B | 7568呎 (4+房)
 $60544万
 $80,000/呎
-(19年-05月-15日)</t>
+(19年-05月)</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
           <t>C | 4214呎 (4+房)
 $45000万
 $106,787/呎
-(21年-10月-20日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -5071,7 +5071,7 @@
           <t>C | 4214呎 (4+房)
 $37505万
 $89,000/呎
-(21年-05月-02日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -5140,7 +5140,7 @@
           <t>C | 4214呎 (4+房)
 $31184万
 $74,000/呎
-(18年-11月-15日)</t>
+(18年-11月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -5171,7 +5171,7 @@
           <t>D | 2865呎 (3房)
 $18622万
 $65,000/呎
-(21年-02月-04日)</t>
+(21年-02月)</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
           <t>C | 4214呎 (4+房)
 $34555万
 $82,000/呎
-(21年-08月-22日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -5194,7 +5194,7 @@
           <t>D | 2865呎 (3房)
 $17960万
 $62,688/呎
-(20年-09月-07日)</t>
+(20年-09月)</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
           <t>C | 4214呎 (4+房)
 $29203万
 $69,300/呎
-(19年-02月-26日)</t>
+(19年-02月)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -5217,7 +5217,7 @@
           <t>D | 2865呎 (3房)
 $18050万
 $63,000/呎
-(20年-11月-26日)</t>
+(20年-11月)</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5232,7 @@
           <t>C | 4214呎 (4+房)
 $28770万
 $68,272/呎
-(18年-11月-07日)</t>
+(18年-11月)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -5240,7 +5240,7 @@
           <t>D | 2865呎 (3房)
 $17500万
 $61,082/呎
-(20年-07月-19日)</t>
+(20年-07月)</t>
         </is>
       </c>
     </row>
@@ -5263,7 +5263,7 @@
           <t>D | 2865呎 (3房)
 $17476万
 $61,000/呎
-(20年-11月-15日)</t>
+(20年-11月)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-寿臣山及浅水湾-深水湾径8号.xlsx
+++ b/files/港岛-寿臣山及浅水湾-深水湾径8号.xlsx
@@ -4646,7 +4646,7 @@
           <t>B | 3641呎 (4+房)
 $39323万
 $108,000/呎
-(22年-01月)</t>
+(22年-01月-05日)</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
           <t>B | 3641呎 (4+房)
 $24941万
 $68,500/呎
-(18年-11月)</t>
+(18年-11月-13日)</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
           <t>B | 3641呎 (4+房)
 $25123万
 $69,000/呎
-(21年-03月)</t>
+(21年-03月-16日)</t>
         </is>
       </c>
     </row>
@@ -4784,7 +4784,7 @@
           <t>B | 3641呎 (4+房)
 $24468万
 $67,200/呎
-(19年-06月)</t>
+(19年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
           <t>A | 3407呎 (4+房)
 $21348万
 $62,660/呎
-(25年-06月)</t>
+(25年-06月-04日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -4807,7 +4807,7 @@
           <t>B | 3641呎 (4+房)
 $22865万
 $62,800/呎
-(19年-02月)</t>
+(19年-02月-26日)</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
           <t>B | 3641呎 (4+房)
 $22865万
 $62,800/呎
-(19年-05月)</t>
+(19年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
           <t>B | 3641呎 (4+房)
 $22137万
 $60,800/呎
-(19年-04月)</t>
+(19年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
           <t>B | 7568呎 (4+房)
 $60544万
 $80,000/呎
-(19年-05月)</t>
+(19年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
           <t>C | 4214呎 (4+房)
 $45000万
 $106,787/呎
-(21年-10月)</t>
+(21年-10月-20日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -5071,7 +5071,7 @@
           <t>C | 4214呎 (4+房)
 $37505万
 $89,000/呎
-(21年-05月)</t>
+(21年-05月-02日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -5140,7 +5140,7 @@
           <t>C | 4214呎 (4+房)
 $31184万
 $74,000/呎
-(18年-11月)</t>
+(18年-11月-15日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -5171,7 +5171,7 @@
           <t>D | 2865呎 (3房)
 $18622万
 $65,000/呎
-(21年-02月)</t>
+(21年-02月-04日)</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
           <t>C | 4214呎 (4+房)
 $34555万
 $82,000/呎
-(21年-08月)</t>
+(21年-08月-22日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -5194,7 +5194,7 @@
           <t>D | 2865呎 (3房)
 $17960万
 $62,688/呎
-(20年-09月)</t>
+(20年-09月-07日)</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
           <t>C | 4214呎 (4+房)
 $29203万
 $69,300/呎
-(19年-02月)</t>
+(19年-02月-26日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -5217,7 +5217,7 @@
           <t>D | 2865呎 (3房)
 $18050万
 $63,000/呎
-(20年-11月)</t>
+(20年-11月-26日)</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5232,7 @@
           <t>C | 4214呎 (4+房)
 $28770万
 $68,272/呎
-(18年-11月)</t>
+(18年-11月-07日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -5240,7 +5240,7 @@
           <t>D | 2865呎 (3房)
 $17500万
 $61,082/呎
-(20年-07月)</t>
+(20年-07月-19日)</t>
         </is>
       </c>
     </row>
@@ -5263,7 +5263,7 @@
           <t>D | 2865呎 (3房)
 $17476万
 $61,000/呎
-(20年-11月)</t>
+(20年-11月-15日)</t>
         </is>
       </c>
     </row>
